--- a/output/長野赤十字病院_随意契約_X線関連.xlsx
+++ b/output/長野赤十字病院_随意契約_X線関連.xlsx
@@ -455,7 +455,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J4"/>
+  <dimension ref="A1:J5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -532,48 +532,94 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
+          <t>X線ｱﾝｷﾞｵｸﾞﾗﾌｨｼｽﾃﾑ（Alphenix Sky）の購入</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>1式</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>事務部管財課長野県長野市若里五丁目22番1号</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>3月29日</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>キャノンメディカルシステムズ株式会社 長野県松本市深志二丁目5番26号松本第一ビル</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="n">
+        <v>105600000</v>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>https://www.nagano-med.jrc.or.jp/wp/wp-content/uploads/R4zuikeikouhyou2.pdf</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>血管撮影（CVS、アンギオ）</t>
+        </is>
+      </c>
+      <c r="I4" s="3" t="inlineStr">
+        <is>
+          <t>製品</t>
+        </is>
+      </c>
+      <c r="J4" s="3" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
           <t>ポータブル撮影装置（島津モバイルアート1号機）の管球交換</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B5" s="3" t="inlineStr">
         <is>
           <t>1式</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="C5" s="3" t="inlineStr">
         <is>
           <t>事務部管財課長野県長野市若里五丁目22番1号</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>令和4年10月21日</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>10月21日</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
         <is>
           <t>丸文通称株式会社 長野県松本市鎌田一丁目11番25号</t>
         </is>
       </c>
-      <c r="F4" s="4" t="n">
+      <c r="F5" s="4" t="n">
         <v>1888590</v>
       </c>
-      <c r="G4" s="3" t="inlineStr">
+      <c r="G5" s="3" t="inlineStr">
         <is>
           <t>https://www.nagano-med.jrc.or.jp/wp/wp-content/uploads/R4zuikeikouhyou2.pdf</t>
         </is>
       </c>
-      <c r="H4" s="3" t="inlineStr">
+      <c r="H5" s="3" t="inlineStr">
         <is>
           <t>回診用X線装置</t>
         </is>
       </c>
-      <c r="I4" s="3" t="inlineStr">
+      <c r="I5" s="3" t="inlineStr">
         <is>
           <t>製品</t>
         </is>
       </c>
-      <c r="J4" s="3" t="inlineStr"/>
+      <c r="J5" s="3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -655,13 +701,9 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="C6" s="3" t="inlineStr">
-        <is>
-          <t>公表された随意契約に該当なし</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="C6" s="3" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
@@ -716,7 +758,7 @@
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>不明（令和3年4月1日〜令和3年4月1日）</t>
+          <t>不明（〜令和3年4月1日）</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -725,13 +767,13 @@
         </is>
       </c>
       <c r="C12" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>不明（令和3年7月26日〜令和3年7月31日）</t>
+          <t>不明（〜）</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
@@ -740,13 +782,13 @@
         </is>
       </c>
       <c r="C13" s="3" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>不明（令和3年8月16日〜令和3年9月22日）</t>
+          <t>不明（〜令和3年9月22日）</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -755,13 +797,13 @@
         </is>
       </c>
       <c r="C14" s="3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>不明（令和3年10月11日〜令和3年11月29日）</t>
+          <t>不明（10月11日〜11月29日）</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
@@ -776,7 +818,7 @@
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>不明（令和3年12月15日〜令和4年1月21日）</t>
+          <t>不明（12月15日〜1月21日）</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -791,7 +833,7 @@
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>不明（令和4年2月1日〜令和4年3月24日）</t>
+          <t>不明（2月1日〜3月24日）</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
@@ -806,7 +848,7 @@
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>不明（令和4年4月1日〜令和5年3月31日）</t>
+          <t>不明（4月1日〜3月31日）</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
@@ -815,13 +857,13 @@
         </is>
       </c>
       <c r="C18" s="3" t="n">
-        <v>67</v>
+        <v>69</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>不明（令和8年5月11日〜令和8年5月25日）</t>
+          <t>不明（5月11日〜5月25日）</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">

--- a/output/長野赤十字病院_随意契約_X線関連.xlsx
+++ b/output/長野赤十字病院_随意契約_X線関連.xlsx
@@ -758,7 +758,7 @@
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>不明（〜令和3年4月1日）</t>
+          <t>不明（令和3年4月1日〜令和3年4月1日）</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -767,13 +767,13 @@
         </is>
       </c>
       <c r="C12" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>不明（〜）</t>
+          <t>不明（令和3年7月26日〜令和3年7月31日）</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
@@ -782,13 +782,13 @@
         </is>
       </c>
       <c r="C13" s="3" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>不明（〜令和3年9月22日）</t>
+          <t>不明（令和3年8月16日〜令和3年9月22日）</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -797,7 +797,7 @@
         </is>
       </c>
       <c r="C14" s="3" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="15">
